--- a/data/numeric/input/old_data_43/第二季度【案卷】.xlsx
+++ b/data/numeric/input/old_data_43/第二季度【案卷】.xlsx
@@ -1,361 +1,334 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sunyixuan/Desktop/syx_result/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sunyixuan/Desktop/syx_result/input/old_data_43/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B282672-F59A-E14B-B472-D38F7428FE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C949B94B-2952-E340-8F9A-28401BD601B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="问题数量汇总" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="97">
   <si>
+    <t>所属市</t>
+  </si>
+  <si>
+    <t>刘*</t>
+  </si>
+  <si>
+    <t>某市7</t>
+  </si>
+  <si>
+    <t>某市1</t>
+  </si>
+  <si>
+    <t>某市6</t>
+  </si>
+  <si>
+    <t>某市8</t>
+  </si>
+  <si>
+    <t>某市11</t>
+  </si>
+  <si>
+    <t>段*</t>
+  </si>
+  <si>
+    <t>某市4</t>
+  </si>
+  <si>
+    <t>某市3</t>
+  </si>
+  <si>
+    <t>某区5</t>
+  </si>
+  <si>
+    <t>官*</t>
+  </si>
+  <si>
+    <t>任*</t>
+  </si>
+  <si>
+    <t>某市5</t>
+  </si>
+  <si>
     <t>第二季度</t>
   </si>
   <si>
+    <t>第二季度问题案卷</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>县区</t>
+  </si>
+  <si>
+    <t>和*****公司</t>
+  </si>
+  <si>
+    <t>某市9</t>
+  </si>
+  <si>
+    <t>某县9</t>
+  </si>
+  <si>
+    <t>某县7</t>
+  </si>
+  <si>
+    <t>李*</t>
+  </si>
+  <si>
+    <t>某县3</t>
+  </si>
+  <si>
+    <t>某区1</t>
+  </si>
+  <si>
+    <t>某县6</t>
+  </si>
+  <si>
+    <t>某县8</t>
+  </si>
+  <si>
+    <t>某县1</t>
+  </si>
+  <si>
+    <t>某县2</t>
+  </si>
+  <si>
+    <t>某市2</t>
+  </si>
+  <si>
+    <t>某区3</t>
+  </si>
+  <si>
+    <t>黄*******公司</t>
+  </si>
+  <si>
+    <t>计数</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>第二季度抽卷数量</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>百分比</t>
+  </si>
+  <si>
+    <t>0.824</t>
+  </si>
+  <si>
+    <t>0.872727272727273</t>
+  </si>
+  <si>
+    <t>0.863636363636364</t>
+  </si>
+  <si>
+    <t>0.824175824175824</t>
+  </si>
+  <si>
+    <t>0.864197530864197</t>
+  </si>
+  <si>
+    <t>0.924242424242424</t>
+  </si>
+  <si>
+    <t>0.879310344827586</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0.517241379310345</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>0.666666666666667</t>
+  </si>
+  <si>
     <t>二季度案卷对比一季度重复出现的县</t>
   </si>
   <si>
-    <t>所属市</t>
-  </si>
-  <si>
-    <t>第二季度问题案卷</t>
-  </si>
-  <si>
-    <t>第二季度抽卷数量</t>
-  </si>
-  <si>
-    <t>百分比</t>
-  </si>
-  <si>
     <t>是否重复出现</t>
   </si>
   <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>时*******公司</t>
+  </si>
+  <si>
+    <t>某区4</t>
+  </si>
+  <si>
+    <t>某县5</t>
+  </si>
+  <si>
+    <t>某区2</t>
+  </si>
+  <si>
+    <t>某县4</t>
+  </si>
+  <si>
+    <t>某县10</t>
+  </si>
+  <si>
+    <t>某市10</t>
+  </si>
+  <si>
     <t>涉及县的数量</t>
   </si>
   <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>0.824</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>石家庄市</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>0.872727272727273</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t>保定市</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>0.863636363636364</t>
-  </si>
-  <si>
-    <t>沧州市</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>0.824175824175824</t>
-  </si>
-  <si>
-    <t>衡水市</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>邢台市</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>0.864197530864197</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>0.924242424242424</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>廊坊市</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>0.879310344827586</t>
-  </si>
-  <si>
-    <t>定州市</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>0.517241379310345</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>雄安新区</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>承德市</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>0.666666666666667</t>
-  </si>
-  <si>
-    <t>县区</t>
-  </si>
-  <si>
-    <t>计数</t>
-  </si>
-  <si>
-    <t>迁安市</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>定兴县</t>
-  </si>
-  <si>
-    <t>香河县</t>
-  </si>
-  <si>
-    <t>丰南区</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>玉田县</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>曲阳县</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>磁县</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>桃城区</t>
-  </si>
-  <si>
-    <t>永年区</t>
-  </si>
-  <si>
-    <t>无极县</t>
-  </si>
-  <si>
-    <t>冀州区</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
-    <t>南皮县</t>
-  </si>
-  <si>
-    <t>平乡县</t>
-  </si>
-  <si>
-    <t>宁晋县</t>
-  </si>
-  <si>
-    <t>鸡泽县</t>
-  </si>
-  <si>
-    <t>遵化市</t>
-  </si>
-  <si>
-    <t>南宫市</t>
-  </si>
-  <si>
-    <t>刘红霞</t>
-  </si>
-  <si>
-    <t>和*****公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>盛*</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘*</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>趋*****公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄*******公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>盛*梅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时*******公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢*兰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>官*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>任*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>段*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>郑*国</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张*华</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>张*</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢*</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>郑*</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -399,9 +372,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -439,7 +412,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -473,6 +446,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -507,9 +481,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -684,531 +659,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="2:7">
       <c r="B18" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="2:7">
       <c r="B19" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="2:7">
       <c r="B21" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="G21" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="B23" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="B24" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
         <v>43</v>
       </c>
-      <c r="F24" t="s">
-        <v>72</v>
-      </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="2:7">
       <c r="B25" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="2:7">
       <c r="B26" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="2:7">
       <c r="B27" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="2:7">
       <c r="B28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="2:7">
       <c r="B30" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="2:7">
       <c r="B31" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="2:7">
       <c r="B32" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="B34" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="B35" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1376,13 +1351,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02227B5F-7B2E-40E8-9327-7CE566973FE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD9D89AF-6437-4745-B066-7974ADEFA779}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F44B61DD-3914-457B-8A03-0034117D146E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{253BEF37-6BC7-4095-8370-F154825CEFE6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4C1A295-EF7A-46B3-AC1F-396C9E4B53D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF04FDCF-1D3E-45D1-BFF6-1B0E77996AC2}"/>
 </file>